--- a/experiments/SENSORES.xlsx
+++ b/experiments/SENSORES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29826"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29923"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nico2\Documentos\UPC\ETSEIB\Q4-2\TFM\Base\GNNs\Github\experiments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nico2\Documentos\UPC\ETSEIB\Q4-2\TFM\Base\GNNs\GitNicole\Github\experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0ADC6F-F0F7-4AC0-ABC2-D0420AFC224D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B26281-7703-49F2-BA09-98FE866A2516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7650" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{63F6C506-AE90-4C76-996B-E158CDA03993}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{63F6C506-AE90-4C76-996B-E158CDA03993}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="107">
   <si>
     <t>0.05</t>
   </si>
@@ -119,15 +119,6 @@
     <t>SEED</t>
   </si>
   <si>
-    <t xml:space="preserve">Cheb 1 </t>
-  </si>
-  <si>
-    <t>Cheb2</t>
-  </si>
-  <si>
-    <t>Gat</t>
-  </si>
-  <si>
     <t>Cheb 2 (no seed)</t>
   </si>
   <si>
@@ -303,13 +294,79 @@
   </si>
   <si>
     <t>No 6-12</t>
+  </si>
+  <si>
+    <t>Gat2 (no seed)</t>
+  </si>
+  <si>
+    <t>Gatv2 (no seed)</t>
+  </si>
+  <si>
+    <t>17-11</t>
+  </si>
+  <si>
+    <t>7-15</t>
+  </si>
+  <si>
+    <t>10-14</t>
+  </si>
+  <si>
+    <t>9-10</t>
+  </si>
+  <si>
+    <t>1-15</t>
+  </si>
+  <si>
+    <t>5-9-11-17</t>
+  </si>
+  <si>
+    <t>3-4-11-15</t>
+  </si>
+  <si>
+    <t>4-5-10-12</t>
+  </si>
+  <si>
+    <t>1-3-16-18</t>
+  </si>
+  <si>
+    <t>9-11-12-19</t>
+  </si>
+  <si>
+    <t>1-2-3-8-9-13-14-18</t>
+  </si>
+  <si>
+    <t>2-6-8-9-12-14-17-18</t>
+  </si>
+  <si>
+    <t>4-5-6-8-9-10-14-19</t>
+  </si>
+  <si>
+    <t>3-5-6-7-12-13-15-17</t>
+  </si>
+  <si>
+    <t>2-4-6-11-12-14-17-18</t>
+  </si>
+  <si>
+    <t>No 13-17</t>
+  </si>
+  <si>
+    <t>No 10-17</t>
+  </si>
+  <si>
+    <t>No 14-18</t>
+  </si>
+  <si>
+    <t>No 3-8</t>
+  </si>
+  <si>
+    <t>No 14-19</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,16 +374,68 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7EAED"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -349,17 +458,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="6" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -694,748 +840,625 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{877AEE59-DA98-48E1-A7CC-EC01C9196807}">
-  <dimension ref="A2:N37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A2:Q33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="5.36328125" customWidth="1"/>
-    <col min="7" max="7" width="19.7265625" customWidth="1"/>
-    <col min="8" max="8" width="19.6328125" customWidth="1"/>
-    <col min="9" max="9" width="21" customWidth="1"/>
-    <col min="10" max="10" width="4.81640625" customWidth="1"/>
-    <col min="11" max="11" width="5.26953125" customWidth="1"/>
-    <col min="12" max="12" width="17.08984375" customWidth="1"/>
-    <col min="13" max="14" width="17.7265625" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" customWidth="1"/>
+    <col min="8" max="8" width="19.73046875" customWidth="1"/>
+    <col min="9" max="10" width="19.59765625" customWidth="1"/>
+    <col min="11" max="11" width="21" customWidth="1"/>
+    <col min="12" max="12" width="4.796875" customWidth="1"/>
+    <col min="13" max="13" width="5.265625" customWidth="1"/>
+    <col min="14" max="14" width="17.06640625" customWidth="1"/>
+    <col min="15" max="17" width="17.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+    <row r="3" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="F3" s="7"/>
+      <c r="G3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="H3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="F4" s="9">
+        <v>1</v>
+      </c>
+      <c r="G4" s="10">
+        <v>8</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="F5" s="9">
+        <v>2</v>
+      </c>
+      <c r="G5" s="10">
+        <v>16</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="F6" s="9">
+        <v>3</v>
+      </c>
+      <c r="G6" s="10">
+        <v>7</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="F7" s="9">
+        <v>4</v>
+      </c>
+      <c r="G7" s="10">
+        <v>12</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="F8" s="9">
+        <v>5</v>
+      </c>
+      <c r="G8" s="10">
+        <v>5</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A13" s="1">
+        <v>1</v>
+      </c>
+      <c r="B13" s="1">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1">
+        <v>4</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="J13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A14" s="1">
         <v>2</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="B14" s="1">
+        <v>10</v>
+      </c>
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1">
+        <v>17</v>
+      </c>
+      <c r="E14" s="1">
+        <v>15</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" s="1">
+        <v>2</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A15" s="1">
+        <v>3</v>
+      </c>
+      <c r="B15" s="1">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1">
+        <v>4</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>3</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M15" s="1">
+        <v>3</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A16" s="1">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1">
+        <v>12</v>
+      </c>
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1">
+        <v>9</v>
+      </c>
+      <c r="E16" s="1">
+        <v>5</v>
+      </c>
+      <c r="G16" s="1">
+        <v>4</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M16" s="1">
+        <v>4</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A17" s="1">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1">
+        <v>8</v>
+      </c>
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>13</v>
+      </c>
+      <c r="G17" s="1">
+        <v>5</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="M17" s="1">
+        <v>5</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="G21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="K21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="M22" s="1">
+        <v>1</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="G23" s="1">
+        <v>2</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="M23" s="1">
+        <v>2</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="G24" s="1">
         <v>3</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
-        <v>1</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1">
-        <v>8</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="s">
+      <c r="H24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="M24" s="1">
+        <v>3</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="G25" s="1">
         <v>4</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="H25" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M25" s="1">
         <v>4</v>
       </c>
-      <c r="K5" s="1">
-        <v>1</v>
-      </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1">
-        <v>16</v>
-      </c>
-      <c r="D6" s="1">
-        <v>16</v>
-      </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="s">
+      <c r="N25" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="G26" s="1">
         <v>5</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="H26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="M26" s="1">
         <v>5</v>
       </c>
-      <c r="K6" s="1">
-        <v>2</v>
-      </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1">
-        <v>7</v>
-      </c>
-      <c r="D7" s="1">
-        <v>7</v>
-      </c>
-      <c r="F7" s="1">
-        <v>3</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K7" s="1">
-        <v>3</v>
-      </c>
-      <c r="L7" s="1"/>
-      <c r="M7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1">
-        <v>12</v>
-      </c>
-      <c r="D8" s="1">
-        <v>12</v>
-      </c>
-      <c r="F8" s="1">
-        <v>4</v>
-      </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K8" s="1">
-        <v>4</v>
-      </c>
-      <c r="L8" s="1"/>
-      <c r="M8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1">
-        <v>5</v>
-      </c>
-      <c r="F9" s="1">
-        <v>5</v>
-      </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" s="1">
-        <v>5</v>
-      </c>
-      <c r="L9" s="1"/>
-      <c r="M9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="F13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K14" s="1">
-        <v>1</v>
-      </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="F15" s="1">
-        <v>2</v>
-      </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K15" s="1">
-        <v>2</v>
-      </c>
-      <c r="L15" s="1"/>
-      <c r="M15" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="F16" s="1">
-        <v>3</v>
-      </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K16" s="1">
-        <v>3</v>
-      </c>
-      <c r="L16" s="1"/>
-      <c r="M16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="F17" s="1">
-        <v>4</v>
-      </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K17" s="1">
-        <v>4</v>
-      </c>
-      <c r="L17" s="1"/>
-      <c r="M17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="F18" s="1">
-        <v>5</v>
-      </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" s="1">
-        <v>5</v>
-      </c>
-      <c r="L18" s="1"/>
-      <c r="M18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
-        <v>1</v>
-      </c>
-      <c r="B24" s="1">
-        <v>3</v>
-      </c>
-      <c r="C24" s="1">
-        <v>8</v>
-      </c>
-      <c r="D24" s="1">
-        <v>16</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K24" s="1">
-        <v>1</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M24" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N24" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="1">
-        <v>2</v>
-      </c>
-      <c r="B25" s="1">
-        <v>10</v>
-      </c>
-      <c r="C25" s="1">
-        <v>9</v>
-      </c>
-      <c r="D25" s="1">
-        <v>17</v>
-      </c>
-      <c r="F25" s="1">
-        <v>2</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K25" s="1">
-        <v>2</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
-        <v>3</v>
-      </c>
-      <c r="B26" s="1">
-        <v>5</v>
-      </c>
-      <c r="C26" s="1">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1">
-        <v>4</v>
-      </c>
-      <c r="F26" s="1">
-        <v>3</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K26" s="1">
-        <v>3</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="1">
-        <v>4</v>
-      </c>
-      <c r="B27" s="1">
-        <v>12</v>
-      </c>
-      <c r="C27" s="1">
-        <v>11</v>
-      </c>
-      <c r="D27" s="1">
-        <v>9</v>
-      </c>
-      <c r="F27" s="1">
-        <v>4</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K27" s="1">
-        <v>4</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="1">
-        <v>5</v>
-      </c>
-      <c r="B28" s="1">
-        <v>8</v>
-      </c>
-      <c r="C28" s="1">
-        <v>12</v>
-      </c>
-      <c r="D28" s="1">
-        <v>2</v>
-      </c>
-      <c r="F28" s="1">
-        <v>5</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K28" s="1">
-        <v>5</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="F32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F33" s="1">
-        <v>1</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K33" s="1">
-        <v>1</v>
-      </c>
-      <c r="L33" s="1" t="s">
+      <c r="N26" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="M33" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F34" s="1">
-        <v>2</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K34" s="1">
-        <v>2</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="N34" s="1" t="s">
+      <c r="O26" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P26" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="35" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F35" s="1">
-        <v>3</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K35" s="1">
-        <v>3</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="36" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F36" s="1">
-        <v>4</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K36" s="1">
-        <v>4</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="37" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F37" s="1">
-        <v>5</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K37" s="1">
-        <v>5</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="Q26" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="17:17" x14ac:dyDescent="0.45">
+      <c r="Q33" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1443,6 +1466,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CE60AC9EA23CDE41B87131422E75FAA1" ma:contentTypeVersion="6" ma:contentTypeDescription="Crea un document nou" ma:contentTypeScope="" ma:versionID="ff08b9f14304db93d2cca2fb5731fecf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="6372d654-5e29-4b2e-a0c2-4d5de6f7b195" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd568e6c590604bc0a462e5faf11a307" ns3:_="">
     <xsd:import namespace="6372d654-5e29-4b2e-a0c2-4d5de6f7b195"/>
@@ -1600,22 +1638,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D772EBA-DA67-4465-9D99-3951E83A4B28}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1505A34-FFC7-425E-B25A-B0CE61285C68}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="6372d654-5e29-4b2e-a0c2-4d5de6f7b195"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ED53D37-DF86-46F1-A0CE-5EE64D8D1281}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1631,28 +1678,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D772EBA-DA67-4465-9D99-3951E83A4B28}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1505A34-FFC7-425E-B25A-B0CE61285C68}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="6372d654-5e29-4b2e-a0c2-4d5de6f7b195"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>